--- a/pof_files/POF-info_待确认与弃用.xlsx
+++ b/pof_files/POF-info_待确认与弃用.xlsx
@@ -85,7 +85,7 @@
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="6" max="6" width="66" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="62" customWidth="1"/>
@@ -125,7 +125,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pof_info_map.py 标记</t>
+          <t xml:space="preserve">标记措辞</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -147,7 +147,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -162,44 +162,44 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.color_mgmt</t>
+          <t xml:space="preserve">（整个 struct 的规则）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 color_mgmt : 1; /* for clear */</t>
+          <t xml:space="preserve">struct vs_plane_info {</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认为 1，cursor layer默认不写，标记为待确认</t>
+          <t xml:space="preserve">总数为POF Pre-processing 中的layer type不为Not Used的layer数 + POF 中Cursor Layer数， cursor layer数由POF中Cursor Layer 决定, 所有layer被平均分到fe0，fe1，还是全分到fe0，由用户决定,需要提醒用户确认，默认是平均分配。即使fe1没有layer，也需要生成plane_fe1_info.单条 FE 最多 8 个，超出即报错。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+          <t xml:space="preserve">—（不是成员，不适用）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 无对应条目</t>
+          <t xml:space="preserve">— layer 如何分到 fe0/fe1 由客户决定，CF 与 POF 都不描述</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">layer 的 color management（clear）总开关。默认写 1、cursor 不写，cursor 这条例外需确认。</t>
+          <t xml:space="preserve">layer 总数 = POF 中 type 不为 Not Used 的 layer 数 + Cursor Layer 数；所有 layer 是平均分到 fe0/fe1 还是全给 fe0，由用户决定（默认平均分，奇数多的那个给 fe0）。即使 fe1 没有 layer 也要生成 plane_fe1_info，单条 FE 最多 8 个。add_cid.py 的 --layer-all-fe0 就是切这个开关的。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -214,44 +214,44 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.gamut_map</t>
+          <t xml:space="preserve">.min_width</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 gamut_map : 1; /* for gamut_map */</t>
+          <t xml:space="preserve">unsigned int min_width; /* for plane min width */</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, 只有8200 使用，待确认</t>
+          <t xml:space="preserve">默认0, cursor layer默认为8，提醒用户确认</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/40 个CID置非零：8200 0x2000002e/0x31b</t>
+          <t xml:space="preserve">16/40 个CID置非零：8200 0x30b/0x310/0x311/0x331/0x335, 9000 0x20000015/0x20000018/0x20000024, 9400 0x2000002b/0x20000035/0x20000036/0x2000003b/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 无（CF 是 DC9X00 专用表，gamut_map 是 8x00 特性）</t>
+          <t xml:space="preserve">❌ CF 无最小尺寸行；cursor 的 8 也无出处</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">色域映射。9x00 已不用，8200 还在用，需确认 9x00 侧能否彻底不写。</t>
+          <t xml:space="preserve">该 layer 允许的最小输入宽度。普通层 0，cursor 层 8 —— cursor 的这个 8 需确认。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -266,44 +266,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.fast_clear</t>
+          <t xml:space="preserve">.min_height</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 fast_clear : 1; /* for wb_dec_decoder_fc */</t>
+          <t xml:space="preserve">unsigned int min_height; /* for plane min height */</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, POF中 Decompresssion Input frame buffer decompression中的字段为DEC400时为1，但如果为cursor layer，也不写，标记为 待确认</t>
+          <t xml:space="preserve">默认0，cursor layer默认为8，提醒用户确认</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9/40 个CID置非零：9000 0x20000015/0x20000018/0x20000024, 9200 0x20000014/0x20000021/0x20000028, 9400 0x2000002b/0x20000036/0x2000003b</t>
+          <t xml:space="preserve">16/40 个CID置非零：8200 0x30b/0x310/0x311/0x331/0x335, 9000 0x20000015/0x20000018/0x20000024, 9400 0x2000002b/0x20000035/0x20000036/0x2000003b/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△ 仅旁证：FE_Layer{i}_Decompress_Cache_Ver / FE_Layer_DeCompress_TFBC_EN，无 fast-clear 行</t>
+          <t xml:space="preserve">❌ 同上</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC400 的 fast clear（整块常量色快速清屏）。只在全局 decompression 恰为 DEC400 时写 1，DEC400A/PVRIC/DECNANO 一律不写，需确认该口径。</t>
+          <t xml:space="preserve">该 layer 允许的最小输入高度，cursor 层 8，同上需确认。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -318,44 +318,44 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.layer_reuse</t>
+          <t xml:space="preserve">.max_width</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 layer_reuse : 1;</t>
+          <t xml:space="preserve">unsigned int max_width; /* for plane max width */</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有9200 0x20000021使用，待确认</t>
+          <t xml:space="preserve">默认4k, 由Layer* 的 Max resolution决定，cursor layer默认为256，提醒用户确认</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9200 0x20000021</t>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ PDMA_EN = 空(=关) 1/34（纵向可复用层数 16→32），与 cmd_list/max_reuse_num* 同族</t>
+          <t xml:space="preserve">✅ FE_Layer{i}_MaxWidth = 4096 (34/34)；cursor 的 256 无出处</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一层寄存器组在纵向被复用多次（PDMA）。与 dc_info 的 cmd_list / plane_normal_num / max_reuse_num0/1 同属一族。</t>
+          <t xml:space="preserve">该 layer 最大输入宽度，取自 POF 的 Layer Max resolution；cursor 固定 256。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -370,287 +370,287 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.palette</t>
+          <t xml:space="preserve">.max_height</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 palette : 1; /* for palette */</t>
+          <t xml:space="preserve">unsigned int max_height; /* for plane max height */</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有9200 0x20000024/03 使用，待确认</t>
+          <t xml:space="preserve">默认4k, 由Layer* 的 Max resolution决定，cursor layer默认为256，提醒用户确认</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9000 0x20000024</t>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 无对应条目</t>
+          <t xml:space="preserve">⚠️ CF 只有宽度行、无高度行（与 4K 只限宽的工程约定一致）</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">调色板（索引色）输入支持。</t>
+          <t xml:space="preserve">该 layer 最大输入高度；POF 只写「4K」时高度按 4320 写，cursor 固定 256。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_be_info[]</t>
+          <t xml:space="preserve">plane_fe0_info[] / plane_fe1_info[]</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_display_info</t>
+          <t xml:space="preserve">vs_plane_info</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.ccm_linear_ex</t>
+          <t xml:space="preserve">.color_mgmt</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 ccm_linear_ex : 1; /* for ccm_lnr_ex */</t>
+          <t xml:space="preserve">u32 color_mgmt : 1; /* for clear */</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有0x200000b/1a使用，标记为待确认</t>
+          <t xml:space="preserve">默认为 1，cursor layer默认不写，标记为待确认</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/40 个CID置非零：9400 0x2000000b/0x2000001a</t>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△ 仅旁证：BE_outCtrl{i}_PostPro_CC_Lnr_Matrix_Share3DLUT_EN 空(=关)，无 ex 档</t>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">线性域 CCM 的扩展版（ccm_lnr_ex）。现网只有两个 CID 用。</t>
+          <t xml:space="preserve">layer 的 color management（clear）总开关。默认 1、cursor 不写，cursor 这条例外需确认。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_be_info[]</t>
+          <t xml:space="preserve">plane_fe0_info[] / plane_fe1_info[]</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_display_info</t>
+          <t xml:space="preserve">vs_plane_info</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.crc_start</t>
+          <t xml:space="preserve">.gamut_map</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 crc_start : 1; /* for crc start configurable *if not, a crc start will control all pipe crc start */</t>
+          <t xml:space="preserve">u32 gamut_map : 1; /* for gamut_map */</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, 只有0x2000001a使用，标记为 待确认</t>
+          <t xml:space="preserve">默认不写, 只有8200 使用，待确认</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
+          <t xml:space="preserve">2/40 个CID置非零：8200 0x2000002e/0x31b</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 的 CRC 行都是取样点，没有 start 控制</t>
+          <t xml:space="preserve">❌ CF 无（CF 是 DC9X00 专用表，gamut_map 是 8x00 特性）</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRC 能否每条 pipe 单独启停。为 0 时一个 crc start 控制所有 pipe。</t>
+          <t xml:space="preserve">色域映射。9x00 已不用、8200 还在用，需确认 9x00 侧能否彻底不写。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_be_info[]</t>
+          <t xml:space="preserve">plane_fe0_info[] / plane_fe1_info[]</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_display_info</t>
+          <t xml:space="preserve">vs_plane_info</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.dbi</t>
+          <t xml:space="preserve">.fast_clear</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 dbi : 1; /* for dbi, dbi_coef */</t>
+          <t xml:space="preserve">u32 fast_clear : 1; /* for wb_dec_decoder_fc */</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有0x2000001a/0b使用，标记为待确认</t>
+          <t xml:space="preserve">默认不写, POF中 Decompresssion Input frame buffer decompression中的字段为DEC400时为1，但如果为cursor layer，也不写，标记为 待确认</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/40 个CID置非零：9400 0x2000000b/0x2000001a</t>
+          <t xml:space="preserve">9/40 个CID置非零：9000 0x20000015/0x20000018/0x20000024, 9200 0x20000014/0x20000021/0x20000028, 9400 0x2000002b/0x20000036/0x2000003b</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△ BE_outif_IF{i}_Command_mode_EN = 1 (25/34)：DBI 即 command mode 接口，语义近但非同一寄存器块</t>
+          <t xml:space="preserve">△ 仅旁证：FE_Layer{i}_Decompress_Cache_Ver / FE_Layer_DeCompress_TFBC_EN，无 fast-clear 行</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DBI（MIPI command mode 接口）及其系数表。</t>
+          <t xml:space="preserve">DEC400 的 fast clear（整块常量色快速清屏）。只在全局 decompression 恰为 DEC400 时写 1，DEC400A/PVRIC/DECNANO 一律不写，需确认该口径。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_be_info[]</t>
+          <t xml:space="preserve">plane_fe0_info[] / plane_fe1_info[]</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_display_info</t>
+          <t xml:space="preserve">vs_plane_info</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.spr</t>
+          <t xml:space="preserve">.layer_reuse</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 spr : 1; /* for spr */</t>
+          <t xml:space="preserve">u32 layer_reuse : 1;</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有0x2000001a使用，标记为待确认</t>
+          <t xml:space="preserve">默认不写，只有9200 0x20000021使用，待确认</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
+          <t xml:space="preserve">1/40 个CID置非零：9200 0x20000021</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 无对应条目</t>
+          <t xml:space="preserve">✅ PDMA_EN = 空(=关) 1/34（纵向可复用层数 16→32），与 cmd_list/max_reuse_num* 同族</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPR（子像素重排），用于 RGB 非标准排布的面板。</t>
+          <t xml:space="preserve">同一层寄存器组在纵向被复用多次（PDMA）。与 dc_info 的 cmd_list / plane_normal_num / max_reuse_num0/1 同族。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_be_info[]</t>
+          <t xml:space="preserve">plane_fe0_info[] / plane_fe1_info[]</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_display_info</t>
+          <t xml:space="preserve">vs_plane_info</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.disp_spr</t>
+          <t xml:space="preserve">.palette</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 disp_spr : 1; /* for display spr point */</t>
+          <t xml:space="preserve">u32 palette : 1; /* for palette */</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有0x2000001a使用，标记为 待确认</t>
+          <t xml:space="preserve">默认不写，只有9200 0x20000024/03 使用，待确认</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
+          <t xml:space="preserve">1/40 个CID置非零：9000 0x20000024</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -660,14 +660,14 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">display 通路上是否存在 SPR 写回点。</t>
+          <t xml:space="preserve">调色板（索引色）输入支持。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140</t>
+          <t xml:space="preserve">85</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -682,510 +682,3318 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.split</t>
+          <t xml:space="preserve">.type</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u32 split : 1; /* for split *the feature is same as spliter, just the different version and usage */</t>
+          <t xml:space="preserve">enum display_type type; /* for display type, 0 : POST_PROCESS * 1 : BLEND_WB_PROCESS, 2 : PATH_SHARED_WB_PROCESS */</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, 标记为 待确认</t>
+          <t xml:space="preserve">POF的PostProc map 为POST_PROCESS, 如果 Scenario为 On-Line&amp;Offline write back，则多加的一个display为PATH_SHARED_WB_PROCESS， 否则多加的一个map为BLEND_WB_PROCESS，待用户确认</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/40 个CID置非零：9200 0x20000028/0x20000037, 9400 0x2000002b/0x20000039/0x2000003b</t>
+          <t xml:space="preserve">24/40 个CID置非零：9000 0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ BE_outif_Splice{i}_EN（老版 Splicer）= 空(=关) 8/34，对上「与 spliter 同功能不同版本」</t>
+          <t xml:space="preserve">✅ BE_outCtrl{i}_Ver = Post_Process（该 pipe 存在时）30/34，印证「PostProc → POST_PROCESS」</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">split：与 spliter 同一能力的另一个硬件版本/用法（vs_type.h 原话）。需确认新芯片用的是哪一版。</t>
+          <t xml:space="preserve">display 类型：POST_PROCESS / BLEND_WB_PROCESS / PATH_SHARED_WB_PROCESS。POF 只说有没有 offline 写回，区分不出后两者。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162</t>
+          <t xml:space="preserve">108</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_wb_info[]</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_wb_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.type</t>
+          <t xml:space="preserve">.gamma</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enum wb_type type; /* for writeback type * 0 : POST_WB, 1 : BLEND_WB, 2 : PATH_SHARED_BLEND_WB */</t>
+          <t xml:space="preserve">u32 gamma : 1; /* for prior_gamma */</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post_write_back* 为 POST_WB, blend_write_back* 且 Scenario为 On-Line&amp;Offline write back为PATH_SHARED_BLEND_WB，否则blend_write_back*为BLEND_WB，待确认, POF无map item, 区分path_shared</t>
+          <t xml:space="preserve">默认为1, PostProc 的 Gamma 为not support时提醒用户确认，若type为非POST_PROCESS，则不写</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">提醒用户确认</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23/37 个CID置非零：9000 0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+          <t xml:space="preserve">36/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x20000014/0x20000021/0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△ BE_Post_WB{i}_Ver = ScreenShot/ForDebug，CF 不区分 BLEND_WB 与 PATH_SHARED_BLEND_WB</t>
+          <t xml:space="preserve">✅ BE_outCtrl{i}_PostPro_CC_Gamma_Prim_EN = 1（默认开，26/34），支持 rule 的「默认写 1」</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">写回类型 POST_WB / BLEND_WB / PATH_SHARED_BLEND_WB。POF 与 CF 都只说有没有 offline 写回，区分不出后两者，故沿用 base。</t>
+          <t xml:space="preserve">输出通路的主 gamma（prior_gamma）。rule 规定 POF 即使写 not support 也仍写 1 并告警——这条「反着写」需要确认。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_wb_info[]</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_wb_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.min_ds_size</t>
+          <t xml:space="preserve">.ccm_linear_ex</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unsigned int min_ds_size; /* for writeback min ds size */</t>
+          <t xml:space="preserve">u32 ccm_linear_ex : 1; /* for ccm_lnr_ex */</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有 9400 0x2000001a 使用，标记为待确认</t>
+          <t xml:space="preserve">默认不写，只有0x200000b/1a使用，标记为待确认</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/37 个CID置非零：9400 0x2000001a</t>
+          <t xml:space="preserve">2/40 个CID置非零：9400 0x2000000b/0x2000001a</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 只有 UV_DownSample_EN 开关，无 downsample 尺寸行</t>
+          <t xml:space="preserve">△ 仅旁证：BE_outCtrl{i}_PostPro_CC_Lnr_Matrix_Share3DLUT_EN 空(=关)，无 ex 档</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">写回 downsample 的最小尺寸限制。</t>
+          <t xml:space="preserve">线性域 CCM 的扩展版（ccm_lnr_ex）。现网只有两个 CID 用。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173</t>
+          <t xml:space="preserve">123</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_wb_info[]</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_wb_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.max_ds_size</t>
+          <t xml:space="preserve">.crc_start</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unsigned int max_ds_size; /* for writeback max ds size */</t>
+          <t xml:space="preserve">u32 crc_start : 1; /* for crc start configurable *if not, a crc start will control all pipe crc start */</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有 9400 0x2000001a 使用，标记为待确认</t>
+          <t xml:space="preserve">默认不写, 只有0x2000001a使用，标记为 待确认</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/37 个CID置非零：9400 0x2000001a</t>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ 同上</t>
+          <t xml:space="preserve">❌ CF 的 CRC 行都是取样点，没有 start 控制</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">写回 downsample 的最大尺寸限制。</t>
+          <t xml:space="preserve">CRC 能否每条 pipe 单独启停。为 0 时一个 crc start 控制所有 pipe。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195</t>
+          <t xml:space="preserve">127</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">crtc_wb_info[]</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_wb_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.stripe</t>
+          <t xml:space="preserve">.dbi</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 stripe : 1; /* for wb_stripe */</t>
+          <t xml:space="preserve">u32 dbi : 1; /* for dbi, dbi_coef */</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，只有 9400 0x2000000b/0x2000001a 使用，标记为待确认</t>
+          <t xml:space="preserve">默认不写，只有0x2000001a/0b使用，标记为待确认</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/37 个CID置非零：9400 0x2000000b/0x2000001a</t>
+          <t xml:space="preserve">2/40 个CID置非零：9400 0x2000000b/0x2000001a</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ CF 无对应条目</t>
+          <t xml:space="preserve">△ BE_outif_IF{i}_Command_mode_EN = 1 (25/34)：DBI 即 command mode 接口，语义近但非同一寄存器块</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">写回分条（stripe）输出。</t>
+          <t xml:space="preserve">DBI（MIPI command mode 接口）及其系数表。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289</t>
+          <t xml:space="preserve">128</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dc_info</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_dc_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.intr_dest</t>
+          <t xml:space="preserve">.spr</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 intr_dest; /* bit0 for NS, bit1 for TZ, bit2 for GSA, bit3 for AOC */</t>
+          <t xml:space="preserve">u32 spr : 1; /* for spr */</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认0x1,标记为 待确认， 客户要求安全feature时写0x03, 不要求时写0x1</t>
+          <t xml:space="preserve">默认不写，只有0x2000001a使用，标记为待确认</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/40 个CID置非零：9400 0x20000005/0x2000000b/0x2000001a/0x20000034/0x20000039/0x32a</t>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">❌ 只有 Intr_Clock_domain = core_clock（时钟域 ≠ 中断目的地）</t>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">中断目的地掩码：bit0 NS / bit1 TZ / bit2 GSA / bit3 AOC。基线只开 NS 故 0x1，客户要安全 feature 时 0x03。</t>
+          <t xml:space="preserve">SPR（子像素重排），用于 RGB 非标准排布的面板。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dc_info</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_dc_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.linear_yuv_rotation</t>
+          <t xml:space="preserve">.disp_spr</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 linear_yuv_rotation : 1; /* for linear yuv rotation */</t>
+          <t xml:space="preserve">u32 disp_spr : 1; /* for display spr point */</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认写0，标记为待确认</t>
+          <t xml:space="preserve">默认不写，只有0x2000001a使用，标记为 待确认</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x2000003b/0x316/0x326/0x327/0x329/0x32a</t>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000001a</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ FE_Layer_DMA_FLIP_ROT90_EN = 1（默认开，10/34），与 rule 的「默认写0」相反；另 FE_DMA_SMPL_Port{i}_MaxWidth_rot = 2160</t>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">linear 排布的 YUV 是否支持旋转。rule 现写「默认写0」，与 CF 的默认开相反，需定夺。</t>
+          <t xml:space="preserve">display 通路上是否存在 SPR 写回点。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">140</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dc_info</t>
+          <t xml:space="preserve">crtc_be_info[]</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_dc_info</t>
+          <t xml:space="preserve">vs_display_info</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.blend_dither_ex</t>
+          <t xml:space="preserve">.split</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 blend_dither_ex : 1; /* for new arch of blend dither, which register named ex */</t>
+          <t xml:space="preserve">u32 split : 1; /* for split *the feature is same as spliter, just the different version and usage */</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, 标记为 待确认，只有 9400 0x2000002b/0x20000035/0x20000036/0x2000003b 使用</t>
+          <t xml:space="preserve">默认不写, 标记为 待确认</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/40 个CID置非零：9400 0x2000002b/0x20000035/0x20000036/0x2000003b</t>
+          <t xml:space="preserve">5/40 个CID置非零：9200 0x20000028/0x20000037, 9400 0x2000002b/0x20000039/0x2000003b</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 只有 BE_Blend{i}_NormalDither_En = 1 (10/34)，CF 没有 ex 架构这一档</t>
+          <t xml:space="preserve">✅ BE_outif_Splice{i}_EN（老版 Splicer）= 空(=关) 8/34，对上「与 spliter 同功能不同版本」</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blend dither 是否为新架构（寄存器名带 ex 的那一版）。</t>
+          <t xml:space="preserve">split：与 spliter 同一能力的另一个硬件版本/用法（vs_type.h 原话）。需确认新芯片用的是哪一版。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">162</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dc_info</t>
+          <t xml:space="preserve">crtc_wb_info[]</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vs_dc_info</t>
+          <t xml:space="preserve">vs_wb_info</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.splice_version</t>
+          <t xml:space="preserve">.type</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 splice_version; /* for splice hw support version */</t>
+          <t xml:space="preserve">enum wb_type type; /* for writeback type * 0 : POST_WB, 1 : BLEND_WB, 2 : PATH_SHARED_BLEND_WB */</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写, 标记为 待确认, POF无map item,，只有 9400 0x2000003b 使用</t>
+          <t xml:space="preserve">Post_write_back* 为 POST_WB, blend_write_back* 且 Scenario为 On-Line&amp;Offline write back为PATH_SHARED_BLEND_WB，否则blend_write_back*为BLEND_WB，待确认, POF无map item, 区分path_shared</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">标记为待确认</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000003b</t>
+          <t xml:space="preserve">23/37 个CID置非零：9000 0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ BE_outif_Splice_EN（新版）= 1（输出口&gt;1）7/34；BE_outif_Splice{i}_EN（老版）= 空 8/34</t>
+          <t xml:space="preserve">△ BE_Post_WB{i}_Ver = ScreenShot/ForDebug，CF 不区分 BLEND_WB 与 PATH_SHARED_BLEND_WB</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">splice 硬件版本：v0 不支持 / v1 只有 ofifo0+1 / v2 ofifo0~3。位于 #ifdef CONFIG_VERISILICON_SPLICE 内。</t>
+          <t xml:space="preserve">写回类型 POST_WB / BLEND_WB / PATH_SHARED_BLEND_WB。POF 与 CF 都只说有没有 offline 写回，区分不出后两者，故沿用 base。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">172</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crtc_wb_info[]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_wb_info</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.min_ds_size</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unsigned int min_ds_size; /* for writeback min ds size */</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写，只有 9400 0x2000001a 使用，标记为待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/37 个CID置非零：9400 0x2000001a</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 只有 UV_DownSample_EN 开关，无 downsample 尺寸行</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写回 downsample 的最小尺寸限制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crtc_wb_info[]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_wb_info</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_ds_size</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unsigned int max_ds_size; /* for writeback max ds size */</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写，只有 9400 0x2000001a 使用，标记为待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/37 个CID置非零：9400 0x2000001a</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ 同上</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写回 downsample 的最大尺寸限制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crtc_wb_info[]</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_wb_info</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.src_mask</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 src_mask; /* for the mask of valid display path */</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post_write_back为所有POST_PROCESS组成的mask，例如有ctrc0 1 2三条POST_PROCESS, 则src_mask为0x7，blend_write_back为最后一个crtc的mask, 标记为需要用户确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35/37 个CID置非零：8200 0x20000008/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目（属连线拓扑，CF 不描述）</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">该写回口能接哪几条 display path 的掩码（bit i = 第 i 条 crtc）。post 写回按所有 POST_PROCESS 组 mask，blend 写回取最后一条 crtc，需按实际连线确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crtc_wb_info[]</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_wb_info</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.stripe</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 stripe : 1; /* for wb_stripe */</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写，只有 9400 0x2000000b/0x2000001a 使用，标记为待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/37 个CID置非零：9400 0x2000000b/0x2000001a</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写回分条（stripe）输出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crtc_wb_info[]</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_wb_info</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.shared_path_id</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 shared_path_id; /* for path shared bld wb, specific the path id which be shared */</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blend_write_back且type为 PATH_SHARED_BLEND_WB时才写, 默认写HW_WB_0, 写默认值需要提醒用户确认，只有 9000 0x20000024, 9400 0x20000034/0x20000039/0x2000003b 使用</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/37 个CID置非零：9000 0x20000024, 9400 0x20000034/0x20000039/0x2000003b</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目（属连线拓扑，CF 不描述）</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATH_SHARED_BLEND_WB 专用：指明共享的是哪一个写回硬件（path id），默认 HW_WB_0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（整个 struct 的规则）</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">struct vs_dc_info {</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只有默认表, 软件维护, 需要找HW确认默认值</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需找 HW 确认默认值</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—（不是成员，不适用）</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— 本条说的「找 HW 确认默认值」，Common Feature 正是那份 HW 基线表</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info 整体只有默认表、由软件维护，POF 说不上话，默认值需要找 HW 确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.name</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const char *name; /* for dc name */</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC 名字字符串，driver 打印与 sysfs 用。必须改成新芯片的名字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.chip_id</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u32 chip_id; /* for chip id */</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">芯片 ID 寄存器期望值，driver probe 时与读到的 HW ID 比对。必须按新芯片改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.revision</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u32 revision; /* for revision */</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">硬件 revision 寄存器期望值。必须按新芯片改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.pid</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u32 pid; /* for pid */</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product ID 寄存器期望值。必须按新芯片改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.cid</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u32 cid; /* for cid */</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chip ID（本工程的 CID，如 0x2000001a），与 drm_configure.sh 传入的一致。必须按新 CID 改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.dc_chip_rev</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 dc_chip_rev; /* for sw version */</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户修改</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户修改</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软件侧维护的 DC 版本号（不是硬件 revision），用于软件分支。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.plane_num</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 plane_num; /* the number of all planes, including cursors */</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有 plane 总数（含 cursor）。写成 ARRAY_SIZE(...)，增删 entry 后自动跟随，只需确认拆分是否合预期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.plane_fe0_num</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 plane_fe0_num; /* number of plane fe0, including cursors */</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">挂在 FE0 上的 plane 数（含 cursor），ARRAY_SIZE 自动跟随。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.plane_fe1_num</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 plane_fe1_num; /* number of plane fe1, including cursors */</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">挂在 FE1 上的 plane 数（含 cursor），单 FE 芯片为 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.planes</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const struct vs_plane_info *planes; /* for planes info */</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认，9x00 无CID使用（仅 8x00/dcnano 使用）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全部 plane 描述数组指针。注意现网 9x00 一个 CID 都没写过这个字段（只有 8x00/dcnano 写）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.format_limit</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const struct format_limit_info *format_limit; /* for format limit info */</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/40 个CID置非零：9200 0x20000014/0x20000021/0x20000028, 9400 0x20000005/0x2000000b/0x2000001a</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">格式级额外约束表（某格式在 src/roi/scaler 场景下的宽高对齐与上下限）。POF 无对应项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.format_limit_size</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 format_limit_size; /* for format limit size */</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/40 个CID置非零：9200 0x20000014/0x20000021/0x20000028, 9400 0x20000005/0x2000000b/0x2000001a</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">format_limit 表条目数，ARRAY_SIZE 自动跟随。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.layer_num</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 layer_num; /* the number of layers excluding cursors */</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">layer 数（不含 cursor），需与 POF 的 Layer 组数一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.layer_fe0_num</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 layer_fe0_num; /* number of layer fe0, excluding cursors*/</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE0 上的 layer 数（不含 cursor）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.layer_fe1_num</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 layer_fe1_num; /* number of layer fe1, excluding cursors*/</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE1 上的 layer 数（不含 cursor）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.display_num</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 display_num; /* number of display */</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">display（crtc）数量，需与 POF 的 PostProc 组数对上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.displays</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const struct vs_display_info *displays; /* for display info */</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">display 描述数组指针（crtc_be_info）。同 .planes，9x00 从不写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.output_num</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 output_num; /* number of output */</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输出接口数量（DP / DSI / DPI…）。POF 描述不到，需按新芯片的 output_info[] 核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.wb_num</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 wb_num; /* number of writeback */</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写回口数量，ARRAY_SIZE(crtc_wb_info) 自动跟随。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.write_back</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const struct vs_wb_info *write_back; /* for writeback info */</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">写回描述数组指针（crtc_wb_info）。同 .planes，9x00 从不写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.dsc_hw_config</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const struct dsc_hw_config *dsc_hw_config; /* for dsc hardware config */</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9/40 个CID置非零：9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— CF 不描述这类（chip id / 计数 / 指针，属软件维护字段）</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DSC（显示流压缩）硬件参数结构指针；不支持 DSC 的芯片应为 NULL。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.pitch_alignment</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 pitch_alignment; /* for pith alignment */</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认64, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">framebuffer 每行字节数的对齐要求，按 DMA 位宽确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.addr_alignment</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 addr_alignment; /* for address alignment */</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认256, 提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">framebuffer 起始地址的对齐要求，按 DMA/MMU 确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe0_dma_sram_size</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 fe0_dma_sram_size; /* for VS_DPU_SPOOL_FE0_DMA SRAM POOL SIZE */</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认512, 提醒用户确认，sram_size = 128 x 活跃端口数</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅ FE_DMA_SMPL_MEM_ALLOC_MaxSize = 「128 KByte × 活跃端口数」(30/34)，与 rule 的公式逐字一致</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE0 DMA SRAM pool 容量（KB）。公式 128 × 活跃端口数，CF 用的是同一条公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe0_scl_sram_size</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 fe0_scl_sram_size; /* for VS_DPU_SPOOL_FE0_SCL SRAM POOL SIZE */</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认120，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 只有 FE_SCL_SMPL_Port{i}_MaxWidth = 4096，没有 scaler SRAM 池容量行</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE0 scaler SRAM pool 容量（KB）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_ext_layer</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 max_ext_layer;</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copy base info, 提醒用户确认是否弃用</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认是否弃用</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最大扩展层（layer_ext）数量。rule 写的是「确认是否弃用」，尚未定论；现网 27/40 个 CID 在用，不像能直接删。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_seg_num</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 max_seg_num; /* number of the max segment */</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认10，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x20000014/0x20000021/0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无 segment 相关条目</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最大 segment 数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_eotf_size</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 max_eotf_size; /* for the max eotf size */</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认129，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000024, 9200 0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ CF 只有 FE_Layer_HDR_OETF_129Entry_EN（**OETF** 的 65/129 档），没有 EOTF 尺寸行 —— 别把那条 129 当成 EOTF 的依据</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOTF LUT 的最大条目数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_tonemap_size</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 max_tonemap_size; /* for the max tonemap size */</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认33，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000024, 9200 0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 只有 BE_outCtrl{i}_PostPro_ToneMapping_Ver = LTM，无表长</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tone mapping LUT 的最大条目数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_degamma_size</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 max_degamma_size; /* for the max degamma size */</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认129，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/40 个CID置非零：8200 0x2000002e/0x31b/0x325, 9000 0x20000015/0x20000018, 9200 0x20000014/0x20000021/0x20000028/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE degamma LUT 的最大条目数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.max_gamma_size</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 max_gamma_size; /* for the max gamma size */</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认257，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335, 9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x20000014/0x20000021/0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334, dcnano 0x20000003/0x20000017/0x20000020</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE gamma LUT 的最大条目数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe_max_gamma_size</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u16 fe_max_gamma_size; /* for the max fe gamma size */</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认65, layer info 中gamma为1才写，只有 9400 0x20000034 使用，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x20000034</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE gamma LUT 的最大条目数，layer 有 gamma 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe_lnr_ccm_bits</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">__u8 fe_lnr_ccm_bits; /* for FE Linear Domain CCM Bits */</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认17，只有 9400 0x2000000b/0x2000001a/0x20000034 使用，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/40 个CID置非零：9400 0x2000000b/0x2000001a/0x20000034</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 只有 FE_Layer{i}_Lnr_Matrix_EN（开关），没有位宽</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE 线性域 CCM 的系数位宽。现网 3 个 CID 写了，取值 16/16/17，与 rule 的默认 17 不完全一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.be_lnr_ccm_bits</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">__u8 be_lnr_ccm_bits; /* for BE Linear Domain CCM Bits */</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认17，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/40 个CID置非零：9400 0x2000000b/0x2000001a/0x20000034/0x20000035/0x20000036</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无 BE 线性域 CCM 位宽行</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE 线性域 CCM 的系数位宽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.be_lnr_ccm_ex_bits</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">__u8 be_lnr_ccm_ex_bits; /* for BE Linear Domain CCM Extesnsion Bits */</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写，只有 9400 0x2000000b/0x2000001a 使用，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/40 个CID置非零：9400 0x2000000b/0x2000001a</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE 线性域 CCM 扩展版的系数位宽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.pre_eotf_bits</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 pre_eotf_bits; /* for FE EOTF module */</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认12，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000024, 9200 0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 只有 BE_Blend_BitDepth = 12（blender 内部运算位深），与 FE EOTF 不是一回事</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE EOTF 模块的位宽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.hdr_bits</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 hdr_bits; /* for the hdr pipeline data bitwidth */</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认24， plane info中hdr为1时才写，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000024, 9200 0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无 HDR 通路位宽行</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDR 通路的数据位宽，layer 有 hdr 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.oetf_bits</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 oetf_bits; /* for FE OETF module */</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认12，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000024, 9200 0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE OETF 模块的位宽。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.pre_degamma_bits</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 pre_degamma_bits; /* for degamma in bits */</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认10, display info中degamma为1时才写，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/40 个CID置非零：9000 0x20000015/0x20000018, 9200 0x20000014/0x20000021/0x20000028/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 的 BE_Gamma_Dither_Bitdepth = 10 是 gamma 之后抖动的目标位深，不是 degamma 输入位宽</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BE degamma 的输入位宽，display 有 degamma 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.cgm_lut_bits</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 cgm_lut_bits; /* for 3DLUT bits */</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认14，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27/40 个CID置非零：8200 0x2000002e/0x311/0x31b/0x325/0x333, 9000 0x20000015/0x20000018/0x20000024, 9200 0x20000014/0x20000021/0x20000028/0x2000002d/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x2000002b/0x20000034/0x20000035/0x20000036/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 只有 BE_outCtrl{i}_PostPro_CC_3DLUT_Table_Ver = Non_shadow（更新方式），无位宽</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3DLUT 的位宽（不是 pipe 位宽：pipe → 3dlut → pipe）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe_pre_degamma_bits</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 fe_pre_degamma_bits; /* for fe degamma in bits */</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认12，plane info中degamma为1时才写，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/40 个CID置非零：9000 0x20000015/0x20000018, 9200 0x20000014/0x20000021/0x20000028, 9400 0x20000034/0x20000039</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无 FE degamma 位宽行</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE degamma 的输入位宽，layer 有 degamma 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe_degamma_bits</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 fe_degamma_bits; /* for fe degamma out bits */</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认17, plane info中degamma为1时才写，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/40 个CID置非零：9000 0x20000015/0x20000018, 9200 0x20000014/0x20000021/0x20000028, 9400 0x20000034/0x20000039</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 的 BE_Gamma_DeGamma_LUT_bitDepth = 17 是 **BE** 侧，不能直接套到 FE</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE degamma 的输出位宽，layer 有 degamma 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.fe_gamma_bits</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 fe_gamma_bits; /* for fe gamma bits */</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认12，plane info中gamma为1时才写，只有 9400 0x20000034 使用，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x20000034</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无对应条目</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE gamma 的位宽，layer 有 gamma 时才写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.intr_dest</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 intr_dest; /* bit0 for NS, bit1 for TZ, bit2 for GSA, bit3 for AOC */</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认0x1,标记为 待确认， 客户要求安全feature时写0x03, 不要求时写0x1</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/40 个CID置非零：9400 0x20000005/0x2000000b/0x2000001a/0x20000034/0x20000039/0x32a</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ 只有 Intr_Clock_domain = core_clock（时钟域 ≠ 中断目的地）</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中断目的地掩码：bit0 NS / bit1 TZ / bit2 GSA / bit3 AOC。基线只开 NS 故 0x1，客户要安全 feature 时 0x03。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.hdr_version</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 hdr_version; /* for HDR hw version */</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写, layer info中hdr为1时写3(V3), 需按实际HDR硬件版本确认3，只有 9200 0x20000028, 9400 0x20000034/0x20000039 使用，提醒用户确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提醒用户确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/40 个CID置非零：9200 0x20000028, 9400 0x20000034/0x20000039</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❌ CF 无 HDR 硬件版本行</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDR 硬件版本：V0 12bit in/24bit out，V1 加 FP16 输入，V2 12bit in/12bit out，V3 由 V1 派生。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.linear_yuv_rotation</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 linear_yuv_rotation : 1; /* for linear yuv rotation */</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认写0，标记为待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x2000003b/0x316/0x326/0x327/0x329/0x32a</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ FE_Layer_DMA_FLIP_ROT90_EN = 1（默认开，10/34），与 rule 的「默认写0」相反；另 FE_DMA_SMPL_Port{i}_MaxWidth_rot = 2160</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linear 排布的 YUV 是否支持旋转。rule 现写「默认写0」，与 CF 的默认开相反，需定夺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.blend_dither_ex</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 blend_dither_ex : 1; /* for new arch of blend dither, which register named ex */</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写, 标记为 待确认，只有 9400 0x2000002b/0x20000035/0x20000036/0x2000003b 使用</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/40 个CID置非零：9400 0x2000002b/0x20000035/0x20000036/0x2000003b</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ 只有 BE_Blend{i}_NormalDither_En = 1 (10/34)，CF 没有 ex 架构这一档</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blend dither 是否为新架构（寄存器名带 ex 的那一版）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.splice_version</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u8 splice_version; /* for splice hw support version */</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认不写, 标记为 待确认, POF无map item,，只有 9400 0x2000003b 使用</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/40 个CID置非零：9400 0x2000003b</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠️ BE_outif_Splice_EN（新版）= 1（输出口&gt;1）7/34；BE_outif_Splice{i}_EN（老版）= 空 8/34</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">splice 硬件版本：v0 不支持 / v1 只有 ofifo0+1 / v2 ofifo0~3。位于 #ifdef CONFIG_VERISILICON_SPLICE 内。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">343</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dc_info</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs_dc_info</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc_info</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs_dc_info</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">.ltm2_mask</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">u8 ltm2_mask; /* for the mask of ltm v2. ltm2 = 0, ltm2_sre = 1, ltm2_foss = 2 */</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">默认不写, PostProc 的 LTM为 support时写0x7，标记为 待确认，只有 9400 0x20000034 使用</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标记为待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1/40 个CID置非零：9400 0x20000034</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">❌ 只有 BE_outCtrl{i}_PostPro_ToneMapping_Ver = LTM，无 ltm2/sre/foss 三位拆分</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LTM v2 的子功能掩码：bit0 ltm2 / bit1 sre / bit2 foss。display 有 ltm 时默认 0x7（三位全开）。</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LTM v2 的子功能掩码：bit0 ltm2 / bit1 sre / bit2 foss。display 有 ltm 时默认 0x7。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J75"/>
 </worksheet>
 </file>
 
@@ -1198,10 +4006,9 @@
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="62" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="6" max="6" width="66" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1237,15 +4044,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pof_info_map.py 标记</t>
+          <t xml:space="preserve">现网使用情况</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">现网使用情况</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">含义 / 备注</t>
         </is>
@@ -1284,15 +4086,10 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">10/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/40 个CID置非零：8200 0x20000008/0x2000002e/0x30b/0x310/0x311/0x31b/0x325/0x331/0x333/0x335</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的 per-plane degamma LUT 尺寸（0 = 无 LUT）。9x00 已改用 dc_info 的 fe_pre_degamma_bits / fe_degamma_bits。</t>
         </is>
@@ -1331,15 +4128,10 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">0/40，无任何CID写过</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0/40，无任何CID写过</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的 per-plane 3D LUT 开关。注意 dc_info.cgm_lut_size 仍按「layer 有 cgm_lut 才写」判断，两者要一起处理。</t>
         </is>
@@ -1378,15 +4170,10 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的 alpha 扩展开关。</t>
         </is>
@@ -1425,15 +4212,10 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">11/40 个CID置非零：9000 0x20000024, 9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11/40 个CID置非零：9000 0x20000024, 9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的 demultiply（预乘 alpha 还原）开关。</t>
         </is>
@@ -1472,15 +4254,10 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">18/40 个CID置非零：9000 0x20000024, 9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18/40 个CID置非零：9000 0x20000024, 9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的 per-plane tone mapping 开关，已由 HDR 通路描述取代。</t>
         </is>
@@ -1519,15 +4296,10 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000015/0x20000018/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028, 9400 0x20000005/0x2000000b/0x2000001a/0x2000002b/0x20000035/0x20000036/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20/40 个CID置非零：9000 0x20000015/0x20000018/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028, 9400 0x20000005/0x2000000b/0x2000001a/0x2000002b/0x20000035/0x20000036/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">旧的压缩输入开关，已由 dc_info.cap_dec 统一描述。</t>
         </is>
@@ -1566,15 +4338,10 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">6/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x32a</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x32a</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">第二个 ROI 区域开关。</t>
         </is>
@@ -1613,15 +4380,10 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
+          <t xml:space="preserve">9/37 个CID置非零：9000 0x2000001b, 9200 0x2000000a/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x32a</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9/37 个CID置非零：9000 0x2000001b, 9200 0x2000000a/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x32a</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">写回压缩开关，已由 cap_dec 统一描述。</t>
         </is>
@@ -1630,7 +4392,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254</t>
+          <t xml:space="preserve">265</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1645,39 +4407,34 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.max_ext_layer</t>
+          <t xml:space="preserve">.cgm_ex_lut_size</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 max_ext_layer;</t>
+          <t xml:space="preserve">u16 cgm_ex_lut_size; /* for roi 3D lut */</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">copy base info, 提醒用户确认是否弃用</t>
+          <t xml:space="preserve">默认729, display info中lut_roi为1时才写, 标记为弃用,TODO:del</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRM 待确认</t>
+          <t xml:space="preserve">10/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27/40 个CID置非零：9000 0x20000015/0x20000018/0x2000001b/0x20000024, 9200 0x2000000a/0x20000014/0x20000021/0x20000028/0x2000002d/0x20000037/0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x20000026/0x2000002b/0x20000034/0x20000035/0x20000036/0x20000039/0x2000003b/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最大扩展层（layer_ext）数量。rule 写的是「确认是否弃用」，尚未定论。</t>
+          <t xml:space="preserve">ROI 3D LUT（9×9×9 = 729）的表长。它与 display.lut_roi 绑定，弃用前要先确认 lut_roi 的去留。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265</t>
+          <t xml:space="preserve">298</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1692,39 +4449,34 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.cgm_ex_lut_size</t>
+          <t xml:space="preserve">.eotf_first</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u16 cgm_ex_lut_size; /* for roi 3D lut */</t>
+          <t xml:space="preserve">u8 eotf_first; /* 0: do not swap Demultiplt and EOTF, 1: swap Demultiplt and EOTF */</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认729, display info中lut_roi为1时才写, 标记为弃用,TODO:del</t>
+          <t xml:space="preserve">默认不写，现网无CID置非零（1 个CID写0）标记为弃用,TODO:del</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">0/40 置非零（1 个CID写了但都是 0）</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROI 3D LUT（9×9×9 = 729）的表长。注意它与 display.lut_roi 绑定，弃用前要先确认 lut_roi 的去留。</t>
+          <t xml:space="preserve">是否交换 Demultiply 与 EOTF 的先后顺序。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1739,84 +4491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">.eotf_first</t>
+          <t xml:space="preserve">.multi_roi</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u8 eotf_first; /* 0: do not swap Demultiplt and EOTF, 1: swap Demultiplt and EOTF */</t>
+          <t xml:space="preserve">u32 multi_roi : 1;</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认不写，现网无CID置非零（1 个CID写0）标记为弃用,TODO:del</t>
+          <t xml:space="preserve">默认不写, 标记为弃用,TODO:del</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK（无标记）</t>
+          <t xml:space="preserve">10/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0/40 置非零（1 个CID写了但都是 0）</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否交换 Demultiply 与 EOTF 的先后顺序。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dc_info</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vs_dc_info</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.multi_roi</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">u32 multi_roi : 1;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">默认不写, 标记为弃用,TODO:del</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEPRECATED 弃用</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/40 个CID置非零：9200 0x323, 9400 0x20000005/0x2000000b/0x2000001a/0x316/0x326/0x327/0x329/0x32a/0x334</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">多 ROI 开关。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:H12"/>
 </worksheet>
 </file>
 
@@ -1856,87 +4556,111 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/POF-info_rule.txt —— 规则文本逐字 copy，未做任何改写</t>
+          <t xml:space="preserve">scripts/POF-info_rule.txt —— 规则文本（-&gt; 之后）逐字 copy，未做任何改写</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">筛选口径</t>
+          <t xml:space="preserve">待确认表口径</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">规则文本（-&gt; 之后）含「待确认」→ 待确认表；含「弃用」→ 弃用表；含「是否弃用」的归入弃用表并单列（尚未定论）</t>
+          <t xml:space="preserve">规则文本含「确认 / 提醒用户 / 核对 / 人工」即收录，覆盖全部措辞变体；具体是哪一种见「标记措辞」列</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pof_info_map.py 标记</t>
+          <t xml:space="preserve">措辞分布</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">同名字段在脚本四张规则表里的 Tag，用来看 rule 与脚本是否同步；出现不一致就是该同步脚本的信号</t>
+          <t xml:space="preserve">提醒用户确认 44 条；标记为待确认 22 条；提醒用户修改 6 条；需找 HW 确认默认值 1 条；提醒用户确认是否弃用 1 条</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">现网使用情况</t>
+          <t xml:space="preserve">弃用表口径</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">遍历 driver/verisilicon/*/info/vs_dc_info_*.c（40 个 CID，跳过 - Copy 文件）。「置非零」= 该 designator 出现且值不是 0/0x0/NULL/false</t>
+          <t xml:space="preserve">含「弃用」且不含「是否弃用」。带「是否」的（.max_ext_layer）尚未定论，按你的要求归入待确认表</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Feature</t>
+          <t xml:space="preserve">struct 级规则</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">对照 DC9X00_Common_Feature_v5.28_20260825.xlsx 的三张数据表。✅=值可印证  ⚠️=有出入需定夺  △=只有旁证  ❌=CF 里查不到</t>
+          <t xml:space="preserve">vs_plane_info（L6，layer 如何分到 fe0/fe1）与 vs_dc_info（L206，默认值需找 HW 确认）这两条挂在 struct 头上、不是成员，也一并收录，成员变量列写「（整个 struct 的规则）」</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CF 的限制</t>
+          <t xml:space="preserve">现网使用情况</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">手上是折叠版（148 个同类族被压成「×N 族」摘要行）；说明 sheet 提到有 _明细 版（425 条 × 11 列），工程目录里没有</t>
+          <t xml:space="preserve">遍历 driver/verisilicon/*/info/vs_dc_info_*.c（40 个 CID，跳过 - Copy 文件）。「置非零」= 该 designator 出现且值不是 0/0x0/NULL/false</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common Feature</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对照 DC9X00_Common_Feature_v5.28_20260825.xlsx 的三张数据表。✅=值可印证  ⚠️=有出入需定夺  △=只有旁证  ❌=CF 里查不到  —=CF 不描述这类</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">CF 的限制</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">手上是折叠版（148 个同类族被压成「×N 族」摘要行）；说明 sheet 提到有 _明细 版（425 条 × 11 列），工程目录里没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">本表统计</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">待确认 20 条，弃用 12 条</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待确认 74 条，弃用 11 条</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B12"/>
 </worksheet>
 </file>